--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/region-de-los-rios.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/region-de-los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1079694-241-CM26</t>
+          <t>1723-473-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>12964.88</v>
+        <v>1174.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1057547-11619-CM26</t>
+          <t>3850-411-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8366.48</v>
+        <v>1432.42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1432083-1874-CM26</t>
+          <t>548867-30-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>998.15</v>
+        <v>1194.69</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1057549-384-CM26</t>
+          <t>1057548-766-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.607.504-7</t>
+          <t>61.607.503-9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LANC</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1029.59</v>
+        <v>1682.33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1057547-11972-CM26</t>
+          <t>1057547-25595-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1428.43</v>
+        <v>8532.200000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1057553-295-CM26</t>
+          <t>1035685-192-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.607.509-8</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>850.75</v>
+        <v>735.74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1057553-296-CM26</t>
+          <t>1432083-861-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.607.509-8</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>816.25</v>
+        <v>867.3099999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1057547-12322-CM26</t>
+          <t>3140-429-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>69.201.100-7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ECOFFICE COMPUTACION LIMITADA</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.293.503-1</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>873.88</v>
+        <v>1393.47</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5658-23-CM26</t>
+          <t>5612-98-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>911.22</v>
+        <v>2382.17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1067355-390-CM26</t>
+          <t>1422032-29-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.980.670-0</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1831.11</v>
+        <v>723.58</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3335-974-CM26</t>
+          <t>5955-398-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>69.201.100-7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4045.34</v>
+        <v>1487.26</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1432083-2044-CM26</t>
+          <t>2905-589-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1042.74</v>
+        <v>1168.31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3335-1060-CM26</t>
+          <t>707424-66-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,27 +1256,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,6 +1301,3056 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
+        <v>1040.88</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3335-1211-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>1051.59</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3335-1214-CM25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>AMINORTE S A</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>99.533.780-0</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>768.72</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1432083-970-CM25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>2226.51</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1432083-971-CM25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>725.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3335-1230-CM25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>COMERCIAL RENHET SPA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>77.619.564-2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>4915.29</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1432083-1040-CM25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>1646.55</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1305560-137-CM25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>2590.62</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>5418-202-CM25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>61.978.900-8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>714.86</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>5740-306-CM25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>61.979.060-k</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>736.0700000000001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1035685-229-CM25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>62.000.400-6</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>837.1900000000001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2281-2734-CM25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>69.200.100-1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>5962.84</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1057548-963-CM25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>61.607.503-9</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>2315.28</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>4777-2284-CM25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>1621.6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>5751-255-CM25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>61.818.002-6</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>1024.23</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3568-769-CM25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>69.201.200-3</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>2180.02</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1218393-2005-CM25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>53.335.808-K</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>CONSULTORIO EXTERNO VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>1385.7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1035685-271-CM25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>62.000.400-6</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>1010.89</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>3335-1590-CM25</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>1089.67</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1497-199-CM25</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>61.601.000-K</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>2188.23</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1497-197-CM25</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>61.601.000-K</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>SURTI VENTAS S.A.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>76.462.500-5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>2266.18</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3789-556-CM25</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>69.200.900-2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>AMINORTE S A</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>99.533.780-0</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>3089.61</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1035685-285-CM25</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>62.000.400-6</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>1051.39</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2908-373-CM25</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>69.200.300-4</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LANCO</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>4435.65</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1422032-70-CM25</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>65.035.343-9</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>763.22</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1432083-1389-CM25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>3697.12</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2905-805-CM25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>69.200.300-4</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LANCO</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>1231.67</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>548867-40-CM25</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>61.979.440-0</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>1084.77</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3850-601-CM25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>69.201.000-0</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>2021.47</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1057548-1121-CM25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>61.607.503-9</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>5222.12</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1426100-167-CM25</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>1253.96</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1057549-500-CM25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>61.607.504-7</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LANC</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>1490.58</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>3334-3743-CM25</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>1446.69</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1057547-34195-CM25</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>2569.88</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1432083-1593-CM25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>77.610.393-4</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>1445.96</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1079694-375-CM25</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>4312.23</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>3335-1908-CM25</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>1019.83</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1057549-529-CM25</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>61.607.504-7</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LANC</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>RED OFFICE SUR LTDA.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>77.806.000-0</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>761.04</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1057547-11619-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>8366.48</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1079694-241-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>12964.88</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1432083-1874-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>78.085.401-4</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>998.15</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1057549-384-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>61.607.504-7</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LANC</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>1029.59</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1057547-11972-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>1428.43</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1057553-295-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>61.607.509-8</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>850.75</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1057553-296-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>61.607.509-8</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>78.085.401-4</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>816.25</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1057547-12322-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>ECOFFICE COMPUTACION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>76.293.503-1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>873.88</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>5658-23-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>61.502.000-1</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>DIRECCION DEL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>911.22</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1067355-390-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>61.980.670-0</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>1831.11</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>3335-974-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>4045.34</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1432083-2044-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>78.085.401-4</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>1042.74</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>3335-1060-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
         <v>1585.27</v>
       </c>
     </row>
